--- a/www/terminologies/CodeSystem-TRE-A02-ProfessionSavFaire-CISIS.xlsx
+++ b/www/terminologies/CodeSystem-TRE-A02-ProfessionSavFaire-CISIS.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="822">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="827">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260730120000</t>
+    <t>20260928120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:00:00+01:00</t>
+    <t>2026-09-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2314,31 +2314,46 @@
     <t>G15_60/SI01</t>
   </si>
   <si>
-    <t>Infirmier - Exercice infirmier en pratique avancée pathologies chroniques stabilisées (SI)</t>
+    <t>Infirmier(ère) en pratique avancée Pathologies chroniques stabilisées (SI)</t>
+  </si>
+  <si>
+    <t>Suivi des patients chroniques (diabète, HTA, insuffisance cardiaque...), prévention, coordination des parcours, en complémentarité avec le médecin et les autres professionnels de santé.</t>
   </si>
   <si>
     <t>G15_60/SI02</t>
   </si>
   <si>
-    <t>Infirmier - Exercice infirmier en pratique avancée oncologie et hémato-oncologie (SI)</t>
+    <t>Infirmier(ère) en pratique avancée Oncologie et hémato-oncologie (SI)</t>
+  </si>
+  <si>
+    <t>Prise en charge des cancers et maladies du sang, administration de traitements, gestion des effets secondaires, en complémentarité avec le médecin et les autres professionnels de santé.</t>
   </si>
   <si>
     <t>G15_60/SI03</t>
   </si>
   <si>
-    <t>Infirmier - Exerc. infirmier pratique avancée maladie rénale chroniq., dialyse, transp. rénale (SI)</t>
+    <t>Infirmier(ère) en pratique avancée Maladie rénale chronique, dialyse, transplantation rénale (SI)</t>
+  </si>
+  <si>
+    <t>Suivi des patients insuffisants rénaux, gestion de la dialyse, accompagnement à la transplantation, en complémentarité avec le médecin et les autres professionnels de santé.</t>
   </si>
   <si>
     <t>G15_60/SI04</t>
   </si>
   <si>
-    <t>Infirmier - Exercice infirmier en pratique avancée santé mentale (SI)</t>
+    <t>Infirmier(ère) en pratique avancée Psychiatrie et santé mentale (SI)</t>
+  </si>
+  <si>
+    <t>Suivi des troubles psychiatriques, entretiens cliniques, prescription de psychotropes, coordination des soins, en complémentarité avec le médecin et les autres professionnels de santé.</t>
   </si>
   <si>
     <t>G15_60/SI05</t>
   </si>
   <si>
-    <t>Infirmier - Exercice infirmier en pratique avancée urgences (SI)</t>
+    <t>Infirmier(ère) en pratique avancée Urgences (SI)</t>
+  </si>
+  <si>
+    <t>Prise en charge des situations d'urgence, gestes techniques, gestion du stress, collaboration avec urgentistes, en complémentarité avec le médecin et les autres professionnels de santé.</t>
   </si>
   <si>
     <t>G15_60/SI06</t>
@@ -7146,68 +7161,78 @@
       <c r="C354" t="s" s="2">
         <v>766</v>
       </c>
-      <c r="D354" s="2"/>
+      <c r="D354" t="s" s="2">
+        <v>767</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="s" s="2">
         <v>61</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C355" t="s" s="2">
-        <v>768</v>
-      </c>
-      <c r="D355" s="2"/>
+        <v>769</v>
+      </c>
+      <c r="D355" t="s" s="2">
+        <v>770</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="s" s="2">
         <v>61</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="C356" t="s" s="2">
-        <v>770</v>
-      </c>
-      <c r="D356" s="2"/>
+        <v>772</v>
+      </c>
+      <c r="D356" t="s" s="2">
+        <v>773</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="s" s="2">
         <v>61</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="C357" t="s" s="2">
-        <v>772</v>
-      </c>
-      <c r="D357" s="2"/>
+        <v>775</v>
+      </c>
+      <c r="D357" t="s" s="2">
+        <v>776</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="s" s="2">
         <v>61</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="C358" t="s" s="2">
-        <v>774</v>
-      </c>
-      <c r="D358" s="2"/>
+        <v>778</v>
+      </c>
+      <c r="D358" t="s" s="2">
+        <v>779</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="s" s="2">
         <v>61</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="C359" t="s" s="2">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="D359" t="s" s="2">
-        <v>777</v>
+        <v>782</v>
       </c>
     </row>
     <row r="360">
@@ -7215,13 +7240,13 @@
         <v>61</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="C360" t="s" s="2">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="D360" t="s" s="2">
-        <v>780</v>
+        <v>785</v>
       </c>
     </row>
     <row r="361">
@@ -7229,13 +7254,13 @@
         <v>61</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="C361" t="s" s="2">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="D361" t="s" s="2">
-        <v>783</v>
+        <v>788</v>
       </c>
     </row>
     <row r="362">
@@ -7243,10 +7268,10 @@
         <v>61</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="C362" t="s" s="2">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="D362" s="2"/>
     </row>
@@ -7255,10 +7280,10 @@
         <v>61</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="C363" t="s" s="2">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="D363" s="2"/>
     </row>
@@ -7267,10 +7292,10 @@
         <v>61</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="C364" t="s" s="2">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="D364" s="2"/>
     </row>
@@ -7279,10 +7304,10 @@
         <v>61</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="C365" t="s" s="2">
-        <v>791</v>
+        <v>796</v>
       </c>
       <c r="D365" s="2"/>
     </row>
@@ -7291,10 +7316,10 @@
         <v>61</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="C366" t="s" s="2">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="D366" s="2"/>
     </row>
@@ -7303,10 +7328,10 @@
         <v>61</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="C367" t="s" s="2">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="D367" s="2"/>
     </row>
@@ -7315,10 +7340,10 @@
         <v>61</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="C368" t="s" s="2">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="D368" s="2"/>
     </row>
@@ -7327,10 +7352,10 @@
         <v>61</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="C369" t="s" s="2">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="D369" s="2"/>
     </row>
@@ -7339,10 +7364,10 @@
         <v>61</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="C370" t="s" s="2">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="D370" s="2"/>
     </row>
@@ -7351,10 +7376,10 @@
         <v>61</v>
       </c>
       <c r="B371" t="s" s="2">
-        <v>802</v>
+        <v>807</v>
       </c>
       <c r="C371" t="s" s="2">
-        <v>803</v>
+        <v>808</v>
       </c>
       <c r="D371" s="2"/>
     </row>
@@ -7363,10 +7388,10 @@
         <v>61</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="C372" t="s" s="2">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="D372" s="2"/>
     </row>
@@ -7375,10 +7400,10 @@
         <v>61</v>
       </c>
       <c r="B373" t="s" s="2">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="C373" t="s" s="2">
-        <v>807</v>
+        <v>812</v>
       </c>
       <c r="D373" s="2"/>
     </row>
@@ -7387,10 +7412,10 @@
         <v>61</v>
       </c>
       <c r="B374" t="s" s="2">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="C374" t="s" s="2">
-        <v>809</v>
+        <v>814</v>
       </c>
       <c r="D374" s="2"/>
     </row>
@@ -7399,10 +7424,10 @@
         <v>61</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>810</v>
+        <v>815</v>
       </c>
       <c r="C375" t="s" s="2">
-        <v>811</v>
+        <v>816</v>
       </c>
       <c r="D375" s="2"/>
     </row>
@@ -7411,10 +7436,10 @@
         <v>61</v>
       </c>
       <c r="B376" t="s" s="2">
-        <v>812</v>
+        <v>817</v>
       </c>
       <c r="C376" t="s" s="2">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="D376" s="2"/>
     </row>
@@ -7423,10 +7448,10 @@
         <v>61</v>
       </c>
       <c r="B377" t="s" s="2">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="C377" t="s" s="2">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="D377" s="2"/>
     </row>
@@ -7435,10 +7460,10 @@
         <v>61</v>
       </c>
       <c r="B378" t="s" s="2">
-        <v>816</v>
+        <v>821</v>
       </c>
       <c r="C378" t="s" s="2">
-        <v>817</v>
+        <v>822</v>
       </c>
       <c r="D378" s="2"/>
     </row>
@@ -7447,10 +7472,10 @@
         <v>61</v>
       </c>
       <c r="B379" t="s" s="2">
-        <v>818</v>
+        <v>823</v>
       </c>
       <c r="C379" t="s" s="2">
-        <v>819</v>
+        <v>824</v>
       </c>
       <c r="D379" s="2"/>
     </row>
@@ -7459,10 +7484,10 @@
         <v>61</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>820</v>
+        <v>825</v>
       </c>
       <c r="C380" t="s" s="2">
-        <v>821</v>
+        <v>826</v>
       </c>
       <c r="D380" s="2"/>
     </row>
